--- a/final/table/workbooks/SuppTable_S3_Species_inventory_and_stability.xlsx
+++ b/final/table/workbooks/SuppTable_S3_Species_inventory_and_stability.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -53,12 +53,12 @@
     <t xml:space="preserve">TG</t>
   </si>
   <si>
+    <t xml:space="preserve">Other</t>
+  </si>
+  <si>
     <t xml:space="preserve">PC</t>
   </si>
   <si>
-    <t xml:space="preserve">Other</t>
-  </si>
-  <si>
     <t xml:space="preserve">DG</t>
   </si>
   <si>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">LPE</t>
   </si>
   <si>
-    <t xml:space="preserve">Category</t>
+    <t xml:space="preserve">SuperClass</t>
   </si>
   <si>
     <t xml:space="preserve">Glycerolipids</t>
@@ -101,13 +101,16 @@
     <t xml:space="preserve">Glycerophospholipids</t>
   </si>
   <si>
+    <t xml:space="preserve">Prenol Lipids</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fatty Acyls</t>
   </si>
   <si>
     <t xml:space="preserve">Sphingolipids</t>
   </si>
   <si>
-    <t xml:space="preserve">Prenol Lipids</t>
+    <t xml:space="preserve">Sterol Lipids</t>
   </si>
   <si>
     <t xml:space="preserve">Condition</t>
@@ -482,7 +485,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>194</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +493,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>190</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4">
@@ -498,7 +501,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>146</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5">
@@ -506,7 +509,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
@@ -514,7 +517,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7">
@@ -522,7 +525,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>238</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -563,10 +566,10 @@
         <v>12</v>
       </c>
       <c r="B3" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C3" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
@@ -574,10 +577,10 @@
         <v>13</v>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="C4" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5">
@@ -728,10 +731,10 @@
         <v>26</v>
       </c>
       <c r="B2" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C2" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3">
@@ -742,7 +745,7 @@
         <v>62</v>
       </c>
       <c r="C3" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4">
@@ -750,10 +753,10 @@
         <v>28</v>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
@@ -761,10 +764,10 @@
         <v>29</v>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -772,10 +775,21 @@
         <v>30</v>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -791,42 +805,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B1" t="s">
         <v>8</v>
       </c>
       <c r="C1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
         <v>394</v>
@@ -850,12 +864,12 @@
         <v>24.3183168834334</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0971425156552499</v>
+        <v>0.0971425156552463</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
@@ -887,7 +901,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
@@ -919,7 +933,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
@@ -951,7 +965,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
@@ -963,19 +977,19 @@
         <v>0.00646658279399933</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0063734697080543</v>
+        <v>0.00637346970805431</v>
       </c>
       <c r="F6" t="n">
         <v>0.00656384679475281</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0000951885433492536</v>
+        <v>0.0000951885433492531</v>
       </c>
       <c r="H6" t="n">
         <v>0.00643757871691847</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00657061954423581</v>
+        <v>0.0065706195442358</v>
       </c>
       <c r="J6" t="n">
         <v>0.00010403675023647</v>
@@ -983,7 +997,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" t="s">
         <v>21</v>
@@ -1015,7 +1029,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B8" t="s">
         <v>23</v>
@@ -1047,7 +1061,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
@@ -1079,7 +1093,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B10" t="s">
         <v>17</v>
@@ -1111,7 +1125,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" t="s">
         <v>18</v>
@@ -1129,7 +1143,7 @@
         <v>1.30688700374538</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00518088791488014</v>
+        <v>0.00518088791488025</v>
       </c>
       <c r="H11" t="n">
         <v>1.29810464202551</v>
@@ -1143,7 +1157,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12" t="s">
         <v>19</v>
@@ -1155,13 +1169,13 @@
         <v>32.6840505592754</v>
       </c>
       <c r="E12" t="n">
-        <v>32.5627687462872</v>
+        <v>32.5627687462873</v>
       </c>
       <c r="F12" t="n">
         <v>32.8185699855265</v>
       </c>
       <c r="G12" t="n">
-        <v>0.127900619619641</v>
+        <v>0.127900619619638</v>
       </c>
       <c r="H12" t="n">
         <v>32.6168550883077</v>
@@ -1170,12 +1184,12 @@
         <v>32.7060672239593</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0671954709677109</v>
+        <v>0.067195470967711</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s">
         <v>16</v>
@@ -1193,10 +1207,10 @@
         <v>2.77042552635474</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0182234092062874</v>
+        <v>0.0182234092062876</v>
       </c>
       <c r="H13" t="n">
-        <v>2.74765586083178</v>
+        <v>2.74765586083179</v>
       </c>
       <c r="I13" t="n">
         <v>2.7544184203489</v>
@@ -1207,7 +1221,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
         <v>11</v>
@@ -1225,7 +1239,7 @@
         <v>2.60270525872856</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0390004689953165</v>
+        <v>0.0390004689953167</v>
       </c>
       <c r="H14" t="n">
         <v>2.52422562035382</v>
@@ -1239,10 +1253,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>363</v>
@@ -1257,7 +1271,7 @@
         <v>23.5010638994004</v>
       </c>
       <c r="G15" t="n">
-        <v>0.205371295387348</v>
+        <v>0.205371295387346</v>
       </c>
       <c r="H15" t="n">
         <v>23.1060120948854</v>
@@ -1266,12 +1280,12 @@
         <v>23.4098046822948</v>
       </c>
       <c r="J15" t="n">
-        <v>0.176448895899995</v>
+        <v>0.176448895899991</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B16" t="s">
         <v>22</v>
@@ -1303,7 +1317,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B17" t="s">
         <v>15</v>
@@ -1335,7 +1349,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B18" t="s">
         <v>20</v>
@@ -1356,7 +1370,7 @@
         <v>0.00197638315333444</v>
       </c>
       <c r="H18" t="n">
-        <v>0.153958721378451</v>
+        <v>0.15395872137845</v>
       </c>
       <c r="I18" t="n">
         <v>0.15474073335733</v>
@@ -1367,7 +1381,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B19" t="s">
         <v>24</v>
@@ -1399,7 +1413,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B20" t="s">
         <v>21</v>
@@ -1417,7 +1431,7 @@
         <v>0.44651909793658</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0014836620515486</v>
+        <v>0.00148366205154862</v>
       </c>
       <c r="H20" t="n">
         <v>0.444276895653474</v>
@@ -1431,7 +1445,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B21" t="s">
         <v>23</v>
@@ -1458,12 +1472,12 @@
         <v>0.0452671437597786</v>
       </c>
       <c r="J21" t="n">
-        <v>0.00050677396758237</v>
+        <v>0.00050677396758238</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B22" t="s">
         <v>14</v>
@@ -1495,7 +1509,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B23" t="s">
         <v>17</v>
@@ -1527,7 +1541,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B24" t="s">
         <v>18</v>
@@ -1559,7 +1573,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B25" t="s">
         <v>19</v>
@@ -1586,12 +1600,12 @@
         <v>30.1771603087944</v>
       </c>
       <c r="J25" t="n">
-        <v>0.112920044604103</v>
+        <v>0.112920044604106</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B26" t="s">
         <v>16</v>
@@ -1623,7 +1637,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B27" t="s">
         <v>11</v>
